--- a/results/momentum_rising_latest.xlsx
+++ b/results/momentum_rising_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:A130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -423,6 +423,909 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>INO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SBMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EDRY</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>GROW</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PPC</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TEAM</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>HQWWW</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AQST</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PRQR</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>DWTX</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>FCUV</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>OMER</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>OBIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>DAAQU</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>GTEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ABOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CELH</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>RCEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CABA</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>AMR</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>INCY</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>IXHL</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>PURR</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>KELYA</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>HALO</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>RDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>USDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>HPK</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>CORT</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ANIX</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>FRNM</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SMJF</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>IOVA</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>APA</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>KGEI</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>GCL</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>PLSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>BYND</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>AMTX</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>RUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>CGEM</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>BFRI</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>DSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>FIGR</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>MINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>PRHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ATRC</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>GWRS</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>PRLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>FDMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>RIGL</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>ACHV</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>CHRD</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>CPRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>SLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>LOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>HTHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>ISNRW</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>YDES</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>BDTX</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ACRV</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>IMMX</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>IPST</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>PAYS</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>FHTX</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>CSTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>ALM</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>LNSR</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>CYPH</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>ARGX</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>BIXIW</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>ETON</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>NBTX</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>NTRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>IVVD</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>PTEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>XNCR</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>LGVN</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>BRR</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>MASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>HTFL</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>FUTU</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>MORN</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>ADIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>KMDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>SBC</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>RDZN</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>CHRN</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>DMLP</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>ORMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>IMCR</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>TOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>BANL</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>ARCT</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>ARX</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>APLM</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>ACON</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>NIQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>AUTL</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>AVAH</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>RNAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>PANL</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>NXPL</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>HWH</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>CRVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>BULLW</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>NCT</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>ALEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>GNLN</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>AIFA</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>NIPG</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>RCMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>IMPP</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>AEHL</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>MF</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>OABI</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>HOWL</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>USDEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>FORTY</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>DFDV</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>VOGX</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>KBSX</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>LEXX</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>NERV</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>DAAQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>HELP</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>PRPO</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>CLYM</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>EXOZ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results/momentum_rising_latest.xlsx
+++ b/results/momentum_rising_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A155"/>
+  <dimension ref="A1:A132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -426,665 +426,665 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RGLD</t>
+          <t>BTCT</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NWGL</t>
+          <t>DH</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MENS</t>
+          <t>PAGP</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ANDG</t>
+          <t>LOT</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>RGLD</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CNDT</t>
+          <t>BMNP</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AUGO</t>
+          <t>GEN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PRE</t>
+          <t>FLXS</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SVRN</t>
+          <t>GALT</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CGEM</t>
+          <t>LIFE</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TOP</t>
+          <t>SUPX</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BDSX</t>
+          <t>EZPW</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MLAB</t>
+          <t>RACD</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>VIR</t>
+          <t>HBIO</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EZRA</t>
+          <t>CHRS</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SWVL</t>
+          <t>MF</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>INMB</t>
+          <t>RFAI</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IXHL</t>
+          <t>GWAV</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RFAI</t>
+          <t>ACTU</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IPSC</t>
+          <t>HHS</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>KEQU</t>
+          <t>AZTR</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>RDI</t>
+          <t>LTGO</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LIFE</t>
+          <t>TMC</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CNXC</t>
+          <t>BLSH</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CSTL</t>
+          <t>VIR</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>USDEW</t>
+          <t>DFDVW</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DCBO</t>
+          <t>HDRN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>LTGO</t>
+          <t>IOND</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>INBX</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AQST</t>
+          <t>TAOX</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>BMNR</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CGEN</t>
+          <t>ANDG</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SAIH</t>
+          <t>NVCT</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>FBLG</t>
+          <t>VOGX</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AZTR</t>
+          <t>BNKK</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HOWL</t>
+          <t>FWDI</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DFDV</t>
+          <t>RDI</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>IMMX</t>
+          <t>GLSI</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ARCT</t>
+          <t>SUJA</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CRBP</t>
+          <t>DCBO</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CELU</t>
+          <t>HNST</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>HSCS</t>
+          <t>SBMT</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MRKR</t>
+          <t>SVRN</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BEEP</t>
+          <t>PROK</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CHTRP</t>
+          <t>OESX</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CARL</t>
+          <t>TII</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>BGC</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DEFT</t>
+          <t>PACB</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>TJGC</t>
+          <t>CYPH</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>GALT</t>
+          <t>CABA</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>TOP</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BTGO</t>
+          <t>HLP</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ANY</t>
+          <t>CAN</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>FLXS</t>
+          <t>METC</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>HBIO</t>
+          <t>BCDA</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PBM</t>
+          <t>RUM</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BLSH</t>
+          <t>COPR</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SBMT</t>
+          <t>CARL</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CLPS</t>
+          <t>HOWL</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PURR</t>
+          <t>IBG</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>KURA</t>
+          <t>NXPL</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BTBD</t>
+          <t>HYPD</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>NAKA</t>
+          <t>DAIC</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>IMC</t>
+          <t>HNRG</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>EOLS</t>
+          <t>BTGO</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PGY</t>
+          <t>CNDT</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STRF</t>
+          <t>MLAB</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AVAH</t>
+          <t>ARCT</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>IDYA</t>
+          <t>MANH</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>EOLS</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>GAUZ</t>
+          <t>HSCS</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>RUM</t>
+          <t>BMEA</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>BMNP</t>
+          <t>BANL</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>FCUV</t>
+          <t>USDEW</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>TAOX</t>
+          <t>PRE</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SUPX</t>
+          <t>NWGL</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ALVO</t>
+          <t>BIVI</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>IQMX</t>
+          <t>MENS</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>TMC</t>
+          <t>GLE</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>DFDVW</t>
+          <t>TEM</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>BANL</t>
+          <t>STRF</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>MANH</t>
+          <t>IXHL</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>MF</t>
+          <t>CNR</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>HNST</t>
+          <t>CTNM</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ODTX</t>
+          <t>EU</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>IOND</t>
+          <t>MTVA</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>METC</t>
+          <t>USDE</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ACB</t>
+          <t>MSTR</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>FBLG</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>NEXT</t>
+          <t>BTCS</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>BTBD</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>AIRE</t>
+          <t>SGML</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>HITI</t>
+          <t>AMR</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>USDE</t>
+          <t>NAKA</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>DOX</t>
         </is>
       </c>
     </row>
@@ -1098,147 +1098,147 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>STRK</t>
+          <t>CELU</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>SPT</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>GLE</t>
+          <t>LHSW</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>SGML</t>
+          <t>CMMB</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>STRD</t>
+          <t>GRI</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>MTC</t>
+          <t>PURR</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>HDRN</t>
+          <t>SBET</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>BIVI</t>
+          <t>DFDV</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>TEM</t>
+          <t>ALVO</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>OESX</t>
+          <t>CADL</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>LOT</t>
+          <t>ASST</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>BCDA</t>
+          <t>CPIX</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>NXPL</t>
+          <t>CNXC</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>GEMI</t>
+          <t>NVA</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>KYNB</t>
+          <t>EML</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>NVCT</t>
+          <t>MRKR</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>HYPD</t>
+          <t>CRML</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>NERV</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>CMMB</t>
+          <t>NCT</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>EZPW</t>
+          <t>MWYN</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>BNKK</t>
+          <t>NWSA</t>
         </is>
       </c>
     </row>
@@ -1252,252 +1252,91 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>AMR</t>
+          <t>PGY</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>SBET</t>
+          <t>SPRB</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>DTCX</t>
+          <t>MTC</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>BMNR</t>
+          <t>ACFN</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>FWDI</t>
+          <t>NGEN</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>BGC</t>
+          <t>DEFT</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>CADL</t>
+          <t>AIRE</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>TII</t>
+          <t>IQMX</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ASST</t>
+          <t>SWVL</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>CRML</t>
+          <t>DTCX</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>CNR</t>
+          <t>TRON</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>TAYD</t>
+          <t>FGNX</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>NWS</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>BTCS</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>XNCR</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>ALM</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>INBX</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>PAGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>SSRM</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>XXI</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>JANX</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>NVA</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>IBG</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>SRRK</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>ACTU</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>CYPH</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>CABA</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>CTNM</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>VOGX</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>TGTX</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>CENN</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>DOX</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>HOOD</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>TRON</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>NGEN</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>BTCT</t>
+          <t>TJGC</t>
         </is>
       </c>
     </row>
